--- a/main/ig/StructureDefinition-eclaire-location.xlsx
+++ b/main/ig/StructureDefinition-eclaire-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-25T15:44:45+00:00</t>
+    <t>2025-11-27T10:20:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -362,7 +362,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -859,7 +859,7 @@
     <t>Physical form of the location.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/location-physical-type</t>
+    <t>http://hl7.org/fhir/ValueSet/location-physical-type|4.0.1</t>
   </si>
   <si>
     <t>.playingEntity [classCode=PLC].code</t>
@@ -947,7 +947,7 @@
     <t>Location.managingOrganization</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -973,7 +973,7 @@
     <t>Location.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(Location|4.0.1)
 </t>
   </si>
   <si>
@@ -1079,7 +1079,7 @@
     <t>Location.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint)
+    <t xml:space="preserve">Reference(Endpoint|4.0.1)
 </t>
   </si>
   <si>
@@ -3725,7 +3725,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
         <v>214</v>
       </c>
@@ -6651,12 +6651,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AL48">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/main/ig/StructureDefinition-eclaire-location.xlsx
+++ b/main/ig/StructureDefinition-eclaire-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-27T10:20:46+00:00</t>
+    <t>2025-11-27T15:06:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
